--- a/daily_matches/job_matches_2026-08-12.xlsx
+++ b/daily_matches/job_matches_2026-08-12.xlsx
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>AI Platform Support Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>UtiliSave, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,81 +482,81 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, PyTorch, Docker, Kubernetes</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, S3, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e54fb12a726038</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe7174599f18e34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Data Engineer – Python / GenAI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>NexonIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, XGBoost, LightGBM, S3, Athena, FastAPI, Docker</t>
+          <t>Data Scientist, Generative AI, LLaMA, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067af6d6bf73eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f37dfee763f8650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Site Reliability Engineer II, GovCloud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Redshift, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=372ed85f15c73051</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Sr. Geospatial Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Planet Fitness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,269 +601,269 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1807b0644dcd10aa</t>
+          <t>https://www.indeed.com/viewjob?jk=07c518ecc45416fd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Solution Architect - Platform, Data Platform &amp; AI Architecture</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Glue, Data Lake, Snowflake, Databricks, PySpark, Hadoop, PostgreSQL, Python, SQL</t>
+          <t>RAG, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=81078f7a7b58a157</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc14d00f76f00ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=76d4fcd88941d6c0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885231374243c77e</t>
+          <t>https://www.indeed.com/viewjob?jk=73bcf871a037a5df</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Internal Audit, Asset Wealth Management - Senior Associate - Data Scientist</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Databricks, Tableau, Python, SQL, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e581cf9916897e</t>
+          <t>https://www.indeed.com/viewjob?jk=a308ff7e1f23007b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Education Data Scientist</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kern Community College District</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Redshift, Hadoop, Tableau, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92745f5caf9a64c2</t>
+          <t>https://www.indeed.com/viewjob?jk=57cbecd8594138e7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c51d45b1b2028d33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a237e06aba32f180</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, AI Infrastructure</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae5da4ec66157e3</t>
+          <t>https://www.indeed.com/viewjob?jk=90833a37168f67a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, AI Infrastructure</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bc7cfc0ee421c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f8bf525ac0051742</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, AI Infrastructure</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>AppFolio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fad6eb1648b21f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b78d864b9beb71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VAS</t>
+          <t>Tecolote Research</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tacoma, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Git, Databricks, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e41222fedf4219</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd213b84056e66e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Quality Engineer</t>
+          <t>Video/Image AI/ML Software Engineer Graduate (Multimedia) - 2027 Start (PhD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, NoSQL, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Cortex, TensorFlow, PyTorch, Python, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f99fdf81883775</t>
+          <t>https://www.indeed.com/viewjob?jk=34f02ded88911306</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-12.xlsx
+++ b/daily_matches/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Platform Support Engineer</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UtiliSave, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, S3, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Cortex, Azure ML, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe7174599f18e34</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Python / GenAI</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NexonIT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LLaMA, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Cortex, Azure ML, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f37dfee763f8650</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II, GovCloud</t>
+          <t>AI Solutions Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ed85f15c73051</t>
+          <t>https://www.indeed.com/viewjob?jk=8e210a1e425e75ec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Geospatial Data Scientist</t>
+          <t>AI Solutions Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Planet Fitness</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c518ecc45416fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca7bcb34dcfe352</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solution Architect - Platform, Data Platform &amp; AI Architecture</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, R, Scala, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81078f7a7b58a157</t>
+          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Senior Business Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d4fcd88941d6c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6018b70e1d02095</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Senior Business Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bcf871a037a5df</t>
+          <t>https://www.indeed.com/viewjob?jk=c072b5d74c6448ef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Senior Business Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a308ff7e1f23007b</t>
+          <t>https://www.indeed.com/viewjob?jk=310da26c1ba6b0f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57cbecd8594138e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51d45b1b2028d33</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,182 +846,427 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a237e06aba32f180</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>AI Product Insights Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, Hugging Face, Prompt Engineering, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90833a37168f67a8</t>
+          <t>https://www.indeed.com/viewjob?jk=aef9b770944f74ff</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Computational Biology MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>LangChain, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8bf525ac0051742</t>
+          <t>https://www.indeed.com/viewjob?jk=148e1bd6969ddcef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Computational Biology MLOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>LangChain, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b78d864b9beb71</t>
+          <t>https://www.indeed.com/viewjob?jk=81d443198f7d02a3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Engineer - Stores &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecolote Research</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tacoma, WA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd213b84056e66e</t>
+          <t>https://www.indeed.com/viewjob?jk=89caa8fcfd13f6cd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Video/Image AI/ML Software Engineer Graduate (Multimedia) - 2027 Start (PhD)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Java Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Cortex, TensorFlow, PyTorch, Python, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34f02ded88911306</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=507d817026273338</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Java Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23f2153bb81c55e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Java Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3f9026fab7d087f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Java Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5c3a7dc608462d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Solutions Architect, Supply Chain</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MSC Industrial Supply Co.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Davidson, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583020299046ba27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a883d0f87526113</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Docker, Git, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=921a30de744ac2c4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-12.xlsx
+++ b/daily_matches/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>PyTorch, OpenCV, Docker, Kubernetes, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>MTS - Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Collinear AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Docker, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a118ca335edc26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer In Test II Atlanta (Remote Friendly)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Redshift, Data Lake, MLflow, Terraform, Snowflake, Databricks, Redshift, PySpark, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,427 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8670ae6971976bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist: III (Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, PostgreSQL, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, FastAPI, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d102224c095a9903</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Science Engineer Internship</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, S3, Glue, Athena, Apache Airflow, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Soteria</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>z/OS Connect API Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=301bbe843fb62e2f</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f27c46253f126087</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Walpole, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46627548f5e20b74</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Walpole, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fd0b788239a8f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Snowflake, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94bd759e42c0aaea</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Snowflake, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b92609a7dfd651b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b3961572d6cebb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ivo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c147857cda96d45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ivo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cdd3cc890630ba9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-12.xlsx
+++ b/daily_matches/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PyTorch, OpenCV, Docker, Kubernetes, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MTS - Engineering</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Collinear AI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a118ca335edc26</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI/LLM Engineer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Data Lake, MLflow, Terraform, Snowflake, Databricks, Redshift, PySpark, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc2db0dfef45423</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, PostgreSQL, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Athena, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Data Lake, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d102224c095a9903</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, S3, Glue, Athena, Apache Airflow, Databricks, PySpark, Python, SQL</t>
+          <t>AI Engineer, RAG, Synapse, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=79d27925e100760a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>z/OS Connect API Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27c46253f126087</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46627548f5e20b74</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd0b788239a8f20</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Snowflake, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, CI/CD, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd759e42c0aaea</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Insights Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Snowflake, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92609a7dfd651b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9c646b378a3d7160</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Engineer – POS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3961572d6cebb5</t>
+          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,777 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c147857cda96d45</t>
+          <t>https://www.indeed.com/viewjob?jk=11ca9778eb4bf8ed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ivo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=051d09280befca99</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Req [5869] Software Engineer, Monetization</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Burbank, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, BigQuery, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2890ba5c12a5a39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Epik Solutions</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Synapse, Data Lake, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=249edf5dfe3b0f0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72a080f84f8173c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=318f8c04eac7f49e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10864f7d0662fedd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09918691f72532fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=390e05d863424c86</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=558e4fff72855bcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA Engineer II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AWeber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc69d8fc387335b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Scientific Business Analyst</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alchemy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e8d2df171f567bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>z/OS Connect API Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48bf9ee522a65045</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Scientific Business Analyst</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Synchron Technologies LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f25e2061436ee94</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Everpure</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, PyTorch, XGBoost, Kubernetes, Snowflake, Kafka, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fdd873ec2d6a992</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Constant Contact</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd215971946494c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>McCormick &amp; Company</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, MLflow, Git, NoSQL, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b507d8e917e04b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Infoville Inc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Paramus, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cdd3cc890630ba9</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b12edc5e4cb11ad8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer I - AI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Chamberlain Group</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5285bcad37e68308</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Gaming Analytics</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Burr Ridge, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a42876e868a8f0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Gaming Analytics</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c3fbbb2fa65fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst, Supplier Performance</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4da74090f039f5e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-12.xlsx
+++ b/daily_matches/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>RAG, Hugging Face, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
+          <t>https://www.indeed.com/viewjob?jk=73529fee08b033be</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI/LLM Engineer - Remote</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, ChromaDB</t>
+          <t>Data Scientist, Copilot, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dc2db0dfef45423</t>
+          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Athena, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer - DataOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Data Lake, FastAPI, Docker, CI/CD</t>
+          <t>RAG, Docker, Apache Airflow, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Synapse, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d27925e100760a</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
+          <t>RAG, Docker, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=709ed70b41dc97a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Digital - Senior Analytics Engineer/Analytics Engineer, Digital Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Aritzia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=0472c3019001bce1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Engineer: DevOps &amp; Application Support</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>AI Engineer, RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e827dc82526b508</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>AI and Agentic AI Risk Management Senior Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Nubank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, CI/CD, Git, Snowflake, Databricks, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=724d20be6015043d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Insights Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Power BI, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c646b378a3d7160</t>
+          <t>https://www.indeed.com/viewjob?jk=15fec4a2dbedda58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – POS</t>
+          <t>Senior Software Developer Contractor</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, S3, Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a581a8d22fa12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ca9778eb4bf8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
+          <t>Data Engineer-Healthcare Practice</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Blue and Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Data Lake, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=58083fed70c8dd26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=051d09280befca99</t>
+          <t>https://www.indeed.com/viewjob?jk=a5de51b55682a2ff</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Req [5869] Software Engineer, Monetization</t>
+          <t>Analytics Engineer - X</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, BigQuery, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2890ba5c12a5a39</t>
+          <t>https://www.indeed.com/viewjob?jk=b144ca98e2d70cdb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer - X</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Epik Solutions</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Synapse, Data Lake, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249edf5dfe3b0f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=642c848a24c55f35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>Analytics Engineer - X</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72a080f84f8173c4</t>
+          <t>https://www.indeed.com/viewjob?jk=35d6af003b368c63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>Analytics Engineer - X</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=318f8c04eac7f49e</t>
+          <t>https://www.indeed.com/viewjob?jk=3009810b143a4e96</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>Senior Software Development Engineer - Iris AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10864f7d0662fedd</t>
+          <t>https://www.indeed.com/viewjob?jk=684ec45978c79e32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>Solutions Architect, Adobe Experience Cloud</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09918691f72532fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7671717365a2b6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>Systems Engineer I - Software, Robotics &amp; Semiconductor Automation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>TensorFlow, PyTorch, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,172 +1266,172 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390e05d863424c86</t>
+          <t>https://www.indeed.com/viewjob?jk=866d1602b03f37e5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>Core States Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558e4fff72855bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=729a95fade64fd4b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QA Engineer II</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AWeber</t>
+          <t>Core States Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc69d8fc387335b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a74393031e32cbb0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Scientific Business Analyst</t>
+          <t>AI Automation Specialist / Agentic Workflow Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>UNIS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Buena Park, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, RAG, LLaMA, Docker, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8d2df171f567bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0fe40867392584d0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>z/OS Connect API Engineer</t>
+          <t>Enterprise Applied AI Solution Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48bf9ee522a65045</t>
+          <t>https://www.indeed.com/viewjob?jk=f82ee3e3ce6f389d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Scientific Business Analyst</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Synchron Technologies LLC</t>
+          <t>MOLG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,287 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f25e2061436ee94</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Everpure</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, XGBoost, Kubernetes, Snowflake, Kafka, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fdd873ec2d6a992</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Constant Contact</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd215971946494c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>McCormick &amp; Company</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Hunt Valley, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Azure ML, MLflow, Git, NoSQL, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b507d8e917e04b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Full-Stack AI Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Infoville Inc</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Paramus, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b12edc5e4cb11ad8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineer I - AI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Chamberlain Group</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5285bcad37e68308</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst - Gaming Analytics</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Burr Ridge, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a42876e868a8f0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst - Gaming Analytics</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c3fbbb2fa65fed</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst, Supplier Performance</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4da74090f039f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=017aa7f38b0d19a1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-12.xlsx
+++ b/daily_matches/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73529fee08b033be</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe Experience Platform)</t>
+          <t>Finance &amp; Strategy AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, PySpark, Python, SQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
+          <t>https://www.indeed.com/viewjob?jk=ada2e929fa9bc025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, BigQuery, Data Lake, CI/CD, Git, Databricks, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - DataOps</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Apache Airflow, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Apache Airflow, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=51bf24e1017c3dfe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Software Engineer I - AWS, React, JavaScript</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=4a462d6021cf94db</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709ed70b41dc97a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Digital - Senior Analytics Engineer/Analytics Engineer, Digital Technology</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0472c3019001bce1</t>
+          <t>https://www.indeed.com/viewjob?jk=263ef3ecd2e448fd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer: DevOps &amp; Application Support</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e827dc82526b508</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d125fc2c299616</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI and Agentic AI Risk Management Senior Specialist</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nubank</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d20be6015043d</t>
+          <t>https://www.indeed.com/viewjob?jk=2772779732bf205a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fec4a2dbedda58</t>
+          <t>https://www.indeed.com/viewjob?jk=d4743ee81678fe7e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Developer Contractor</t>
+          <t>Applications Engineering, Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a581a8d22fa12</t>
+          <t>https://www.indeed.com/viewjob?jk=7172bb43d3b1817b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Synapse, Apache Airflow, CI/CD, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Practice</t>
+          <t>Construction AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue and Company</t>
+          <t>Kokosing Construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Data Lake, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, Copilot, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58083fed70c8dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=19a3263faea4458f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5de51b55682a2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c5baa1b801251575</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer - X</t>
+          <t>Data Scientist - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Persist Brands</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b144ca98e2d70cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e821393222b5b2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer - X</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>RAG, CI/CD, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642c848a24c55f35</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer - X</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>Cortex, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d6af003b368c63</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer - X</t>
+          <t>AWS Cloud Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>RAG, S3, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3009810b143a4e96</t>
+          <t>https://www.indeed.com/viewjob?jk=33627c5062e9bd85</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Iris AI</t>
+          <t>QA Automation Engineer(Order Management Systems)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684ec45978c79e32</t>
+          <t>https://www.indeed.com/viewjob?jk=e643daa84ddfde7e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Architect, Adobe Experience Cloud</t>
+          <t>Platform Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Aspira</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, R, Scala</t>
+          <t>Prompt Engineering, S3, Athena, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7671717365a2b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b3c83c431168a1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Systems Engineer I - Software, Robotics &amp; Semiconductor Automation</t>
+          <t>Python / GenAI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866d1602b03f37e5</t>
+          <t>https://www.indeed.com/viewjob?jk=51feee66d4124263</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Python / GenAI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Core States Group</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,157 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729a95fade64fd4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Core States Group</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>King of Prussia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a74393031e32cbb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Automation Specialist / Agentic Workflow Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>UNIS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Buena Park, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, LLaMA, Docker, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fe40867392584d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Enterprise Applied AI Solution Specialist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Weston, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f82ee3e3ce6f389d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MOLG</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=017aa7f38b0d19a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b680bbc3043e6876</t>
         </is>
       </c>
     </row>
